--- a/sources/nina_step8.xlsx
+++ b/sources/nina_step8.xlsx
@@ -13367,11 +13367,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
@@ -13429,11 +13424,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
@@ -13491,11 +13481,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
@@ -13553,11 +13538,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
@@ -13615,11 +13595,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
@@ -13677,11 +13652,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
@@ -13737,11 +13707,6 @@
       <c r="U152" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">

--- a/sources/nina_step8.xlsx
+++ b/sources/nina_step8.xlsx
@@ -425,7 +425,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col hidden="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col hidden="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
@@ -9411,22 +9411,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step]</t>
+          <t>Creeping Snake</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step]</t>
+          <t>Creeping Snake</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9518,7 +9523,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]&lt;4</t>
+          <t>df+3,2&lt;4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9528,7 +9533,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Roundhouse</t>
+          <t>Creeping Snake – Roundhouse</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9615,7 +9620,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3</t>
+          <t>df+3,2,d+3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9625,7 +9630,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick</t>
+          <t>Creeping Snake – Low Spin Kick</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9717,7 +9722,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3,2</t>
+          <t>df+3,2,d+3,2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9727,7 +9732,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick – Upper</t>
+          <t>Creeping Snake – Low Spin Kick – Upper</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9824,7 +9829,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3,4</t>
+          <t>df+3,2,d+3,4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9834,7 +9839,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick – High Kick</t>
+          <t>Creeping Snake – Low Spin Kick – High Kick</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9921,7 +9926,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3</t>
+          <t>df+3,2,3,3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9931,7 +9936,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo</t>
+          <t>Creeping Snake – Spike Combo</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10018,7 +10023,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3,2</t>
+          <t>df+3,2,3,3,2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -10028,7 +10033,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – Upper</t>
+          <t>Creeping Snake – Spike Combo – Upper</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10125,7 +10130,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3,4</t>
+          <t>df+3,2,3,3,4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -10135,7 +10140,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – High Kick</t>
+          <t>Creeping Snake – Spike Combo – High Kick</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10222,7 +10227,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3,d+4</t>
+          <t>df+3,2,3,3,d+4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -10232,7 +10237,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – Shin Kick</t>
+          <t>Creeping Snake – Spike Combo – Shin Kick</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10319,7 +10324,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3&lt;4</t>
+          <t>df+3,2,3&lt;4</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -10329,7 +10334,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Head Ringer</t>
+          <t>Creeping Snake – Head Ringer</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10416,7 +10421,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],1&lt;4</t>
+          <t>df+3,2,1&lt;4</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -10426,7 +10431,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Biting Snake</t>
+          <t>Creeping Snake – Biting Snake</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11774,27 +11779,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>d+4,1 [~U_~D]</t>
+          <t>d+4,1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [Side Step]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [Side Step]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">

--- a/sources/nina_step8.xlsx
+++ b/sources/nina_step8.xlsx
@@ -928,6 +928,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
@@ -995,6 +1000,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
@@ -1055,6 +1065,11 @@
       <c r="U9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>75937ef0-ab7d-422f-82fa-406485f60d4e</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -13325,6 +13340,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
+        </is>
+      </c>
       <c r="Z145" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
@@ -13377,6 +13397,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
+        </is>
+      </c>
       <c r="Z146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
@@ -13434,6 +13459,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
+        </is>
+      </c>
       <c r="Z147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
@@ -13491,6 +13521,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
+        </is>
+      </c>
       <c r="Z148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
@@ -13548,6 +13583,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
+        </is>
+      </c>
       <c r="Z149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
@@ -13605,6 +13645,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
+        </is>
+      </c>
       <c r="Z150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
@@ -13662,6 +13707,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
+        </is>
+      </c>
       <c r="Z151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
@@ -13719,6 +13769,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
+        </is>
+      </c>
       <c r="Z152" t="inlineStr">
         <is>
           <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
@@ -13781,6 +13836,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
+        </is>
+      </c>
       <c r="Z153" t="inlineStr">
         <is>
           <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
@@ -13838,6 +13898,11 @@
           <t>Initial throw does no damage when doing the Shoulder Buster.</t>
         </is>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
+        </is>
+      </c>
       <c r="Z154" t="inlineStr">
         <is>
           <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
@@ -13895,6 +13960,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
+        </is>
+      </c>
       <c r="Z155" t="inlineStr">
         <is>
           <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
@@ -13962,6 +14032,11 @@
           <t>CH</t>
         </is>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
+        </is>
+      </c>
       <c r="Z156" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
@@ -14014,6 +14089,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
+        </is>
+      </c>
       <c r="Z157" t="inlineStr">
         <is>
           <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
@@ -14071,6 +14151,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>42ce7230-87bf-452a-b714-833a0716e519</t>
+        </is>
+      </c>
       <c r="Z158" t="inlineStr">
         <is>
           <t>42ce7230-87bf-452a-b714-833a0716e519</t>
@@ -14133,6 +14218,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
+        </is>
+      </c>
       <c r="Z159" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
@@ -14185,6 +14275,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
+        </is>
+      </c>
       <c r="Z160" t="inlineStr">
         <is>
           <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
@@ -14242,6 +14337,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
+        </is>
+      </c>
       <c r="Z161" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
@@ -14299,6 +14399,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
+        </is>
+      </c>
       <c r="Z162" t="inlineStr">
         <is>
           <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
@@ -14356,6 +14461,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>f956b41d-482e-44be-a215-575d5455d551</t>
+        </is>
+      </c>
       <c r="Z163" t="inlineStr">
         <is>
           <t>f956b41d-482e-44be-a215-575d5455d551</t>
@@ -14413,6 +14523,11 @@
           <t>Front</t>
         </is>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>55a9a5db-779c-4431-878f-621fd1035127</t>
+        </is>
+      </c>
       <c r="Z164" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
@@ -14465,6 +14580,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
+        </is>
+      </c>
       <c r="Z165" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
@@ -14522,6 +14642,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
+        </is>
+      </c>
       <c r="Z166" t="inlineStr">
         <is>
           <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
@@ -14579,6 +14704,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
+        </is>
+      </c>
       <c r="Z167" t="inlineStr">
         <is>
           <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
@@ -14636,6 +14766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>55349cf9-9743-4042-9932-3196803d0f29</t>
+        </is>
+      </c>
       <c r="Z168" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
@@ -14693,6 +14828,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
+        </is>
+      </c>
       <c r="Z169" t="inlineStr">
         <is>
           <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
@@ -14748,6 +14888,11 @@
       <c r="U170" t="inlineStr">
         <is>
           <t>1+2</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>4d4ecd62-8ffe-41f7-b612-20d6890a6862</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
@@ -14952,6 +15097,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
+        </is>
+      </c>
       <c r="Z174" t="inlineStr">
         <is>
           <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
@@ -14999,6 +15149,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
+        </is>
+      </c>
       <c r="Z175" t="inlineStr">
         <is>
           <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
@@ -15046,6 +15201,11 @@
           <t>hhhhhllmlm</t>
         </is>
       </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
+        </is>
+      </c>
       <c r="Z176" t="inlineStr">
         <is>
           <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
@@ -15093,6 +15253,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
+        </is>
+      </c>
       <c r="Z177" t="inlineStr">
         <is>
           <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
@@ -15140,6 +15305,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
+        </is>
+      </c>
       <c r="Z178" t="inlineStr">
         <is>
           <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
@@ -15187,6 +15357,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
+        </is>
+      </c>
       <c r="Z179" t="inlineStr">
         <is>
           <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
@@ -15234,6 +15409,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
+        </is>
+      </c>
       <c r="Z180" t="inlineStr">
         <is>
           <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
@@ -15281,6 +15461,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
+        </is>
+      </c>
       <c r="Z181" t="inlineStr">
         <is>
           <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
@@ -15328,6 +15513,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
+        </is>
+      </c>
       <c r="Z182" t="inlineStr">
         <is>
           <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
@@ -15380,6 +15570,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>f37af239-8d33-4787-93e6-4352245294b9</t>
+        </is>
+      </c>
       <c r="Z183" t="inlineStr">
         <is>
           <t>f37af239-8d33-4787-93e6-4352245294b9</t>
@@ -15432,6 +15627,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
+        </is>
+      </c>
       <c r="Z184" t="inlineStr">
         <is>
           <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
@@ -15482,6 +15682,11 @@
       <c r="S185" t="inlineStr">
         <is>
           <t>hhhhhllmlm</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>d4f56864-b1c5-4ee6-a66e-c349919b767a</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
